--- a/List of Amendments.xlsx
+++ b/List of Amendments.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="428" documentId="11_5B49236C46998830B07D8232B90A249EA9806F8F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E091479-EB21-4D62-9355-DB2F2200BE7C}"/>
+  <xr:revisionPtr revIDLastSave="440" documentId="11_5B49236C46998830B07D8232B90A249EA9806F8F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21FB3E27-7193-4D91-9D30-A2D60F705543}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12525" yWindow="-21600" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="67">
   <si>
     <t>Document</t>
   </si>
@@ -272,12 +272,44 @@
   <si>
     <t>To give offerors more time to ask questions</t>
   </si>
+  <si>
+    <t>Section H.10</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Added H.10 </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Price Reduction for Orders Exceeding the GSA Simplified Acquisition Threshold</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - Pursuant to Guide, Vol. 14, §§ 310.50.40(c), 310.50.56, the Court’s Contracting Officer is seeking price reductions for all pricing requested in this RFQ.  The Tax Court requires that any such price reductions be included in the offeror’s response to this RFQ.</t>
+    </r>
+  </si>
+  <si>
+    <t>To meet the Guide to Judiciary Policy requirement that the CO seeks a price reduction when the order exceeds the GSA’s simplified acquisition threshold.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -307,6 +339,14 @@
     </font>
     <font>
       <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -665,7 +705,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:F26"/>
+  <dimension ref="B2:F27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.6640625" customWidth="1"/>
@@ -693,20 +733,22 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
-        <v>45716</v>
+        <v>45722</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F3" s="4"/>
+        <v>65</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="4" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B4" s="6">
@@ -716,10 +758,10 @@
         <v>50</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="F4" s="4"/>
     </row>
@@ -731,44 +773,44 @@
         <v>50</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" spans="2:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B6" s="6">
         <v>45716</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" ht="57.6" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="2:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B7" s="6">
         <v>45716</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>42</v>
+      <c r="C7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F7" s="4"/>
+        <v>62</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="8" spans="2:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B8" s="6">
@@ -777,49 +819,47 @@
       <c r="C8" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="2:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="B9" s="6">
+        <v>45716</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E9" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F9" s="4" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="B9" s="6">
-        <v>45710</v>
-      </c>
-      <c r="C9" s="4" t="s">
+    <row r="10" spans="2:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="B10" s="6">
+        <v>45710</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D10" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F9" s="1"/>
-    </row>
-    <row r="10" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B10" s="6">
-        <v>45710</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="F10" s="1"/>
+    </row>
+    <row r="11" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B11" s="6">
         <v>45710</v>
       </c>
@@ -830,13 +870,13 @@
         <v>7</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6" ht="43.2" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B12" s="6">
         <v>45710</v>
       </c>
@@ -844,31 +884,31 @@
         <v>6</v>
       </c>
       <c r="D12" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B13" s="6">
+        <v>45710</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="2"/>
-    </row>
-    <row r="13" spans="2:6" ht="72" x14ac:dyDescent="0.3">
-      <c r="B13" s="6">
-        <v>45710</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="2:6" ht="72" x14ac:dyDescent="0.3">
       <c r="B14" s="6">
         <v>45710</v>
       </c>
@@ -876,16 +916,16 @@
         <v>14</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="2:6" ht="100.8" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B15" s="6">
         <v>45710</v>
       </c>
@@ -893,16 +933,16 @@
         <v>14</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" ht="100.8" x14ac:dyDescent="0.3">
       <c r="B16" s="6">
         <v>45710</v>
       </c>
@@ -910,14 +950,16 @@
         <v>14</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F16" s="5"/>
-    </row>
-    <row r="17" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17" s="6">
         <v>45710</v>
       </c>
@@ -925,12 +967,12 @@
         <v>14</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F17" s="1"/>
+        <v>25</v>
+      </c>
+      <c r="F17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B18" s="6">
@@ -940,16 +982,14 @@
         <v>14</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6" ht="72" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+      <c r="F18" s="1"/>
+    </row>
+    <row r="19" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B19" s="6">
         <v>45710</v>
       </c>
@@ -957,14 +997,16 @@
         <v>14</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F19" s="1"/>
-    </row>
-    <row r="20" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" ht="72" x14ac:dyDescent="0.3">
       <c r="B20" s="6">
         <v>45710</v>
       </c>
@@ -972,10 +1014,10 @@
         <v>14</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F20" s="1"/>
     </row>
@@ -987,14 +1029,14 @@
         <v>14</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F21" s="1"/>
     </row>
-    <row r="22" spans="2:6" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B22" s="6">
         <v>45710</v>
       </c>
@@ -1002,29 +1044,29 @@
         <v>14</v>
       </c>
       <c r="D22" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F22" s="1"/>
+    </row>
+    <row r="23" spans="2:6" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="6">
+        <v>45710</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E23" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F22" s="1"/>
-    </row>
-    <row r="23" spans="2:6" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="B23" s="6">
-        <v>45710</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="F23" s="1"/>
     </row>
-    <row r="24" spans="2:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="B24" s="6">
         <v>45710</v>
       </c>
@@ -1032,14 +1074,14 @@
         <v>39</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F24" s="1"/>
     </row>
-    <row r="25" spans="2:6" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:6" ht="72" x14ac:dyDescent="0.3">
       <c r="B25" s="6">
         <v>45710</v>
       </c>
@@ -1047,14 +1089,14 @@
         <v>39</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F25" s="1"/>
     </row>
-    <row r="26" spans="2:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="B26" s="6">
         <v>45710</v>
       </c>
@@ -1062,300 +1104,34 @@
         <v>39</v>
       </c>
       <c r="D26" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F26" s="1"/>
+    </row>
+    <row r="27" spans="2:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="B27" s="6">
+        <v>45710</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D27" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E27" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F26" s="1"/>
+      <c r="F27" s="1"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:F8">
-    <sortCondition ref="C3:C8"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:F9">
+    <sortCondition ref="C3:C9"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="61" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010042D09E6983C2574185054B40F6DAA347" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a1293ce191f69c072463674441166c75">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b78dfdc0-6d86-4ad7-b6c6-ada07d3cdd19" xmlns:ns3="166c149d-d99b-4c96-9f05-42527fae8239" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="778ee70f84a6111b1044bb4160bce134" ns2:_="" ns3:_="">
-    <xsd:import namespace="b78dfdc0-6d86-4ad7-b6c6-ada07d3cdd19"/>
-    <xsd:import namespace="166c149d-d99b-4c96-9f05-42527fae8239"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b78dfdc0-6d86-4ad7-b6c6-ada07d3cdd19" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="14" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="18" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="19" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="21" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="ab9dc224-b70f-41e7-81fe-c01715919c3d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="23" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="24" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="166c149d-d99b-4c96-9f05-42527fae8239" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="12" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="13" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="22" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ce6b3d55-fb92-47f1-9496-e18defffdc77}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="166c149d-d99b-4c96-9f05-42527fae8239">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b78dfdc0-6d86-4ad7-b6c6-ada07d3cdd19">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="166c149d-d99b-4c96-9f05-42527fae8239" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3E5F9FF-C8EF-4730-B59E-FE3AF9EFFC87}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CC55301-2A79-4F06-A179-E92B9B5DA669}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DA5EDE6-E519-458C-A54E-0927097FD15E}"/>
 </file>